--- a/assets/files/templates/SafePlum_edu_log.xlsx
+++ b/assets/files/templates/SafePlum_edu_log.xlsx
@@ -4143,17 +4143,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
